--- a/basedatos_partidas/salida/descompuestos/07.06.01.190.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.06.01.190.xlsx
@@ -567,7 +567,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-SOPORTE-AC</t>
+          <t>MT-PERNO-ANCLA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -577,17 +577,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Soporte metálico galvanizado para unidad condensadora, con sus anclajes.</t>
+          <t>Perno de anclaje de acero con tuerca y arandela, para fijación de placa base.</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>64</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>113.2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>117.42</v>
+        <v>62.22</v>
       </c>
       <c r="H22" t="n">
-        <v>1.17</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="23">
@@ -788,7 +788,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>118.59</v>
+        <v>62.84</v>
       </c>
     </row>
   </sheetData>
